--- a/registers/Variation Project Register.xlsx
+++ b/registers/Variation Project Register.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ProjectRegister" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProjectRegister" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -189,6 +189,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Setup notes</author>
+    <author>Variation Cover Sheet</author>
   </authors>
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
@@ -244,6 +245,11 @@
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
         <t>Yes or No. The flow filters on this so a finished project can be retired without deleting its history. Change to Yes/No after import.</t>
+      </text>
+    </comment>
+    <comment ref="L4" authorId="1" shapeId="0">
+      <text>
+        <t>The project manager's email. Prints in the letterhead and under the sign-off of every variation for this project.</t>
       </text>
     </comment>
   </commentList>
@@ -251,9 +257,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProjectRegister" displayName="ProjectRegister" ref="A4:K8" headerRowCount="1">
-  <autoFilter ref="A4:K8"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProjectRegister" displayName="ProjectRegister" ref="A4:L8" headerRowCount="1">
+  <autoFilter ref="A4:L8"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="Title"/>
     <tableColumn id="2" name="State"/>
     <tableColumn id="3" name="HeadContractor"/>
@@ -265,6 +271,7 @@
     <tableColumn id="9" name="SiteUrl"/>
     <tableColumn id="10" name="ClauseRef"/>
     <tableColumn id="11" name="Active"/>
+    <tableColumn id="12" name="PmEmail"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -559,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -573,6 +580,7 @@
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -645,6 +653,11 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>PmEmail</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -699,6 +712,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>ben.smith@axisplumbing.com.au</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -750,6 +768,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>jo.tran@axisplumbing.com.au</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -800,6 +823,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>ben.smith@axisplumbing.com.au</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -846,13 +874,16 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="L8" s="4" t="inlineStr"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>After import, fix three column types: State → Choice · RecipientAddress → Multiple lines of text (plain) · Active → Yes/No.</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/registers/Variation Project Register.xlsx
+++ b/registers/Variation Project Register.xlsx
@@ -252,14 +252,19 @@
         <t>The project manager's email. Prints in the letterhead and under the sign-off of every variation for this project.</t>
       </text>
     </comment>
+    <comment ref="M4" authorId="1" shapeId="0">
+      <text>
+        <t>Optional. The project's agreed schedule of rates (Excel), as its path in the site or its full address. Blank = the master rates. See docs/AGREED-RATES.md.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProjectRegister" displayName="ProjectRegister" ref="A4:L8" headerRowCount="1">
-  <autoFilter ref="A4:L8"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProjectRegister" displayName="ProjectRegister" ref="A4:M8" headerRowCount="1">
+  <autoFilter ref="A4:M8"/>
+  <tableColumns count="13">
     <tableColumn id="1" name="Title"/>
     <tableColumn id="2" name="State"/>
     <tableColumn id="3" name="HeadContractor"/>
@@ -272,6 +277,7 @@
     <tableColumn id="10" name="ClauseRef"/>
     <tableColumn id="11" name="Active"/>
     <tableColumn id="12" name="PmEmail"/>
+    <tableColumn id="13" name="RatesFile"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -566,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -581,6 +587,7 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -658,6 +665,11 @@
           <t>PmEmail</t>
         </is>
       </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>RatesFile</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -717,6 +729,11 @@
           <t>ben.smith@axisplumbing.com.au</t>
         </is>
       </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>/Shared Documents/25-135 Warrnambool Hospital/Agreed Schedule of Rates.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -773,6 +790,7 @@
           <t>jo.tran@axisplumbing.com.au</t>
         </is>
       </c>
+      <c r="M6" s="4" t="n"/>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -828,6 +846,7 @@
           <t>ben.smith@axisplumbing.com.au</t>
         </is>
       </c>
+      <c r="M7" s="4" t="n"/>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -875,6 +894,7 @@
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="n"/>
     </row>
     <row r="9"/>
     <row r="10">
@@ -883,7 +903,6 @@
           <t>After import, fix three column types: State → Choice · RecipientAddress → Multiple lines of text (plain) · Active → Yes/No.</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/registers/Variation Project Register.xlsx
+++ b/registers/Variation Project Register.xlsx
@@ -262,9 +262,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProjectRegister" displayName="ProjectRegister" ref="A4:M8" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProjectRegister" displayName="ProjectRegister" ref="A4:N8" headerRowCount="1">
   <autoFilter ref="A4:M8"/>
-  <tableColumns count="13">
+  <tableColumns count="14">
     <tableColumn id="1" name="Title"/>
     <tableColumn id="2" name="State"/>
     <tableColumn id="3" name="HeadContractor"/>
@@ -278,6 +278,7 @@
     <tableColumn id="11" name="Active"/>
     <tableColumn id="12" name="PmEmail"/>
     <tableColumn id="13" name="RatesFile"/>
+    <tableColumn id="14" name="ProjectNumber"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
@@ -572,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -588,6 +589,7 @@
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -670,6 +672,11 @@
           <t>RatesFile</t>
         </is>
       </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>ProjectNumber</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -734,6 +741,11 @@
           <t>/Shared Documents/25-135 Warrnambool Hospital/Agreed Schedule of Rates.xlsx</t>
         </is>
       </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>25-135</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -791,6 +803,11 @@
         </is>
       </c>
       <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>24-902</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -847,6 +864,11 @@
         </is>
       </c>
       <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>25-018</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -895,8 +917,12 @@
       </c>
       <c r="L8" s="4" t="inlineStr"/>
       <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>25-204</t>
+        </is>
+      </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
